--- a/docs/sablonlar/urun-listesi-sablonu.xlsx
+++ b/docs/sablonlar/urun-listesi-sablonu.xlsx
@@ -269,8 +269,9 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Satın alınan = tedarikçiden gelir, raftan sayılır.
-Üretilen = kantinde hazırlanır (tost, çay, poğaça). Üretilen ürünler stoktan ve sayımdan çıkarılır; dönem satış adedi sayım ekranında ayrıca girilir.</t>
+        <t>Satın alınan = tedarikçiden gelir, raftan sayılır, doğrudan satılır.
+Hammadde = raftan sayılır ama satılmaz; reçetelerde tüketilir (ekmek, kaşar, çay).
+Üretilen = kantinde hazırlanır (tost, çay, poğaça). Stoktan ve sayımdan çıkarılır; dönem satış adedi sayım ekranında girilir, maliyeti reçetesinden hesaplanır.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
@@ -696,7 +697,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="42" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>4. Ürün tipi</t>
@@ -704,7 +705,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Tost, çay, poğaça gibi kantinde HAZIRLANAN ürünler için "Üretilen" seçin. Bunlar raftan sayılamadığı için stok ve sayım dışında tutulur; dönem satış adetleri sayım ekranında ayrıca girilir.</t>
+          <t>Tost, çay, poğaça gibi kantinde HAZIRLANAN ürünler için "Üretilen" seçin; bunların içine giren ekmek, kaşar, çay gibi kalemler için "Hammadde" seçin. Hammadde sayıma girer ama satılmaz (satış fiyatını 0 bırakın); tüketimi uygulamadaki Reçeteler ekranından tanımlanır.</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9136,7 @@
       <formula1>"ADET,KG,LT,PAKET,KUTU,PORSIYON"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E401" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz değer" error="Lütfen listeden bir değer seçin." promptTitle="Ürün Tipi" prompt="Kantinde hazırlanan ürünler için 'Üretilen' seçin." type="list">
-      <formula1>"Satın alınan,Üretilen"</formula1>
+      <formula1>"Satın alınan,Hammadde,Üretilen"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H401" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Geçersiz değer" error="Lütfen listeden bir değer seçin." promptTitle="KDV Oranı" prompt="Tedarikçi faturasındaki KDV oranı." type="list">
       <formula1>"1,10,20"</formula1>
